--- a/TEngine/Configs/GameConfig/Datas/item.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADB5C68-4E17-404F-BFC4-EAE82E120B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8C22F2-53F0-4838-BAA3-1BDC99448663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29325" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -119,15 +119,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Common_hint_button</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>重置道具</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Common_reset_button</t>
+    <t>下一关道具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_prop_clear</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_prop_next</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_prop_tip</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -521,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -712,7 +720,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
@@ -720,10 +728,21 @@
         <v>10002</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>10003</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
